--- a/duoki_editor/resources/data/blank/海洋-一般疑问句_肯定答句跟读-1-blank.xlsx
+++ b/duoki_editor/resources/data/blank/海洋-一般疑问句_肯定答句跟读-1-blank.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="47">
   <si>
     <t>stage_id</t>
   </si>
@@ -91,6 +91,9 @@
     <t>一般疑问句_跟读_3_答</t>
   </si>
   <si>
+    <t>一般疑问句_跟读_帮助</t>
+  </si>
+  <si>
     <t>结束语_1</t>
   </si>
   <si>
@@ -103,16 +106,16 @@
     <t>duoki</t>
   </si>
   <si>
-    <t>{npc2_name}，海洋嘉年华巡游开始了！哇，参加巡游的动物朋友们都好可爱啊，你看那边，{sentence_question_cn}？{sentence_question_en}?</t>
+    <t>{npc2_name}，海洋嘉年华巡游开始了！哇，参加巡游的动物朋友们都好可爱啊，你看那边，{sentence_question_cn} {sentence_question_en}</t>
   </si>
   <si>
     <t>快看这边，这边！它是飞鱼吗？Is it a flying fish？</t>
   </si>
   <si>
-    <t>{sentence_answer_en_1}。 {sentence_answer_cn_1} 。</t>
-  </si>
-  <si>
-    <t>{sentence_answer_en_2}。 {sentence_answer_cn_2}。{user_name}，我们也邀请一些海洋朋友组成巡游队吧！</t>
+    <t xml:space="preserve">{sentence_answer_en_1} {sentence_answer_cn_1} </t>
+  </si>
+  <si>
+    <t>{sentence_answer_en_2}  {sentence_answer_cn_2}{user_name}，我们也邀请一些海洋朋友组成巡游队吧！</t>
   </si>
   <si>
     <t>哇，我超喜欢嘉年华巡游的！我们快来邀请参加巡游的朋友吧！第一位朋友是{word_cn}吧！"[{word_en}]"</t>
@@ -127,31 +130,31 @@
     <t>我来帮你吧！"[{word_en}]"</t>
   </si>
   <si>
-    <t>Hooray！ {user_name}，我们的巡游队伍也超棒的！它们都是谁呢？{sentence_question_cn}？{sentence_question_en}?</t>
-  </si>
-  <si>
-    <t>那这位动物朋友呢？{sentence_question_cn}？{sentence_question_en}?</t>
-  </si>
-  <si>
-    <t>这个呢？这个呢？{sentence_question_cn}？{sentence_question_en}?</t>
+    <t>Hooray！ {user_name}，我们的巡游队伍也超棒的！它们都是谁呢？{sentence_question_cn} {sentence_question_en}</t>
+  </si>
+  <si>
+    <t>那这位动物朋友呢？{sentence_question_cn} {sentence_question_en}</t>
+  </si>
+  <si>
+    <t>这个呢？这个呢？{sentence_question_cn} {sentence_question_en}</t>
   </si>
   <si>
     <t>{sentence_answer_en_1}</t>
   </si>
   <si>
-    <t>{sentence_question_en}? {sentence_question_cn}？我知道应该怎么回答，请试着跟我，{sentence_answer_en_1}。</t>
-  </si>
-  <si>
-    <t>别着急，跟我说，{sentence_answer_en_1}。</t>
-  </si>
-  <si>
-    <t>最后一个啦，快跟我说，{sentence_answer_en_1}。</t>
-  </si>
-  <si>
-    <t>我来帮你。{sentence_answer_en_1}。</t>
-  </si>
-  <si>
-    <t>{sentence_answer_en_2}。 太开心了！{user_name}，这10颗亮晶晶的宝石送给你，和你一起参加嘉年华巡游是非常特别的经历！</t>
+    <t>{sentence_question_en} {sentence_question_cn}我知道应该怎么回答，请试着跟我说，{sentence_answer_en_1}</t>
+  </si>
+  <si>
+    <t>别着急，跟我说，{sentence_answer_en_1}</t>
+  </si>
+  <si>
+    <t>最后一个啦，快跟我说，{sentence_answer_en_1}</t>
+  </si>
+  <si>
+    <t>我来帮你。{sentence_answer_en_1}</t>
+  </si>
+  <si>
+    <t>太开心了！{user_name}，这10颗亮晶晶的宝石送给你，和你一起参加嘉年华巡游是非常特别的经历！</t>
   </si>
 </sst>
 </file>
@@ -540,10 +543,10 @@
         <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -557,10 +560,10 @@
         <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -574,10 +577,10 @@
         <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -591,10 +594,10 @@
         <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -608,10 +611,10 @@
         <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -625,10 +628,10 @@
         <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -642,10 +645,10 @@
         <v>16</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -659,10 +662,10 @@
         <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -676,10 +679,10 @@
         <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -693,10 +696,10 @@
         <v>19</v>
       </c>
       <c r="D11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -710,10 +713,10 @@
         <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -727,10 +730,10 @@
         <v>21</v>
       </c>
       <c r="D13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -744,10 +747,10 @@
         <v>22</v>
       </c>
       <c r="D14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -761,10 +764,10 @@
         <v>23</v>
       </c>
       <c r="D15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -778,10 +781,10 @@
         <v>24</v>
       </c>
       <c r="D16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -792,13 +795,13 @@
         <v>8</v>
       </c>
       <c r="C17" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D17" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -809,13 +812,13 @@
         <v>9</v>
       </c>
       <c r="C18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
